--- a/output/yearly_benthic_cover_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_16_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.90171491685147</v>
+        <v>45.8025857915228</v>
       </c>
       <c r="M2" t="n">
-        <v>98.83498518482079</v>
+        <v>98.62154691756766</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99850893093908</v>
+        <v>87.88667804994832</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90169482900591</v>
+        <v>45.83025897996025</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228677189836695</v>
+        <v>2.228444092243481</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689408966919677</v>
+        <v>5.642577711680765</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428923966122316</v>
+        <v>0.7428146974144938</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96404654673574</v>
+        <v>33.94040094444508</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17305024416265</v>
+        <v>34.16947608106671</v>
       </c>
       <c r="I3" t="n">
-        <v>6.557356107845628</v>
+        <v>6.520372664257194</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643077478826447</v>
+        <v>4.642591858840587</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00149106906093</v>
+        <v>12.11332195005169</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86143300187079</v>
+        <v>48.82234103547232</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646188999376</v>
+        <v>106.7659219654843</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.10147546136537</v>
+        <v>86.80201670835841</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63873553439811</v>
+        <v>42.37518341867408</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185513678734881</v>
+        <v>2.175173085434642</v>
       </c>
       <c r="E4" t="n">
-        <v>6.491872811010046</v>
+        <v>6.415192672692334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444492073867335</v>
+        <v>0.7443678986862555</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30625388530059</v>
+        <v>33.12905488640417</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24466353978974</v>
+        <v>34.24092333956775</v>
       </c>
       <c r="I4" t="n">
-        <v>5.47591479297629</v>
+        <v>5.445005458784162</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652807546167084</v>
+        <v>4.652299366789097</v>
       </c>
       <c r="K4" t="n">
-        <v>12.89852453863463</v>
+        <v>13.19798329164159</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28059114619379</v>
+        <v>44.24571182678829</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81785121922653</v>
+        <v>99.81887853710397</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.95122203113876</v>
+        <v>85.40563820018058</v>
       </c>
       <c r="C5" t="n">
-        <v>42.33837987345234</v>
+        <v>41.82366079320402</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129404149903198</v>
+        <v>2.106098324623406</v>
       </c>
       <c r="E5" t="n">
-        <v>7.087096525890153</v>
+        <v>6.969064345104014</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457690023094897</v>
+        <v>0.7456884847595829</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45116968663549</v>
+        <v>32.07700916300676</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30537410623653</v>
+        <v>34.30167029894081</v>
       </c>
       <c r="I5" t="n">
-        <v>4.571352295729593</v>
+        <v>4.545554553998607</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66105626443431</v>
+        <v>4.660553029747393</v>
       </c>
       <c r="K5" t="n">
-        <v>14.04877796886124</v>
+        <v>14.59436179981944</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46073341343707</v>
+        <v>43.43072725534365</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84789125575065</v>
+        <v>99.84874984836711</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.56584186687581</v>
+        <v>83.85180854218532</v>
       </c>
       <c r="C6" t="n">
-        <v>41.66296924154896</v>
+        <v>40.97535768088721</v>
       </c>
       <c r="D6" t="n">
-        <v>2.061700832607805</v>
+        <v>2.02963221225554</v>
       </c>
       <c r="E6" t="n">
-        <v>7.497630752004422</v>
+        <v>7.348317641756566</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746890514913237</v>
+        <v>0.7468130478793268</v>
       </c>
       <c r="G6" t="n">
-        <v>31.41940132176176</v>
+        <v>30.91238918377473</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3569636860089</v>
+        <v>34.35340020244903</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815189041371966</v>
+        <v>3.793674704824328</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668065718207731</v>
+        <v>4.667581549245792</v>
       </c>
       <c r="K6" t="n">
-        <v>15.43415813312418</v>
+        <v>16.14819145781469</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77589061711216</v>
+        <v>42.75018545702038</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8730179917853</v>
+        <v>99.87373459572227</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.95850529511127</v>
+        <v>82.04844813694746</v>
       </c>
       <c r="C7" t="n">
-        <v>40.6481742163799</v>
+        <v>39.76069094498725</v>
       </c>
       <c r="D7" t="n">
-        <v>1.983367048842962</v>
+        <v>1.941280952294683</v>
       </c>
       <c r="E7" t="n">
-        <v>7.743325384005042</v>
+        <v>7.556017279441429</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478458698280067</v>
+        <v>0.747773459184226</v>
       </c>
       <c r="G7" t="n">
-        <v>30.2256293883011</v>
+        <v>29.56675202040329</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40091001208831</v>
+        <v>34.3975791224744</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183390905620817</v>
+        <v>3.165461183248021</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674036686425042</v>
+        <v>4.673584119901412</v>
       </c>
       <c r="K7" t="n">
-        <v>17.04149470488872</v>
+        <v>17.95155186305254</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20435360535993</v>
+        <v>42.18237733904843</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89402252662856</v>
+        <v>99.89462014708823</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.7005739520574</v>
+        <v>86.91927108860294</v>
       </c>
       <c r="C8" t="n">
-        <v>42.88990127057699</v>
+        <v>42.03080721064757</v>
       </c>
       <c r="D8" t="n">
-        <v>1.987560239080433</v>
+        <v>1.94548116001168</v>
       </c>
       <c r="E8" t="n">
-        <v>9.531629178133025</v>
+        <v>9.368323506818077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494269488331887</v>
+        <v>0.7493913619664679</v>
       </c>
       <c r="G8" t="n">
-        <v>30.71196177414899</v>
+        <v>30.05855016757058</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47363964632668</v>
+        <v>34.47200265045753</v>
       </c>
       <c r="I8" t="n">
-        <v>5.562437735327656</v>
+        <v>5.641826229488183</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68391843020743</v>
+        <v>4.683696012290424</v>
       </c>
       <c r="K8" t="n">
-        <v>12.29942604794259</v>
+        <v>13.08072891139706</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62564926267503</v>
+        <v>44.70080901874313</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81497658119461</v>
+        <v>99.81234514078776</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.46953196845612</v>
+        <v>84.66411987230012</v>
       </c>
       <c r="C9" t="n">
-        <v>41.52209695316763</v>
+        <v>40.65018195638179</v>
       </c>
       <c r="D9" t="n">
-        <v>1.885968292006461</v>
+        <v>1.842846806938502</v>
       </c>
       <c r="E9" t="n">
-        <v>9.818390441425382</v>
+        <v>9.659135342789481</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507842195268118</v>
+        <v>0.750781094212851</v>
       </c>
       <c r="G9" t="n">
-        <v>29.14215375839762</v>
+        <v>28.47280371359426</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53607409823334</v>
+        <v>34.53593033379115</v>
       </c>
       <c r="I9" t="n">
-        <v>4.64375978682393</v>
+        <v>4.710240742143571</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692401372042574</v>
+        <v>4.692381838830318</v>
       </c>
       <c r="K9" t="n">
-        <v>14.53046803154389</v>
+        <v>15.33588012769989</v>
       </c>
       <c r="L9" t="n">
-        <v>43.79292285597382</v>
+        <v>43.85722052065477</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84548784068534</v>
+        <v>99.84328260473643</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.17202819836106</v>
+        <v>82.30159915017585</v>
       </c>
       <c r="C10" t="n">
-        <v>39.94475957832009</v>
+        <v>39.01724633848632</v>
       </c>
       <c r="D10" t="n">
-        <v>1.782652527601827</v>
+        <v>1.736694992280172</v>
       </c>
       <c r="E10" t="n">
-        <v>9.926494891133506</v>
+        <v>9.757990809524125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519504359927144</v>
+        <v>0.7519765585712773</v>
       </c>
       <c r="G10" t="n">
-        <v>27.54570916030577</v>
+        <v>26.83271091194158</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58972005566486</v>
+        <v>34.59092169427876</v>
       </c>
       <c r="I10" t="n">
-        <v>3.87581090270792</v>
+        <v>3.931450692509453</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699690224954464</v>
+        <v>4.699853491070482</v>
       </c>
       <c r="K10" t="n">
-        <v>16.82797180163895</v>
+        <v>17.69840084982416</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09827529262919</v>
+        <v>43.15351279107445</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87100667258822</v>
+        <v>99.86915997938492</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.79152804676548</v>
+        <v>79.83034253127065</v>
       </c>
       <c r="C11" t="n">
-        <v>38.16461393325879</v>
+        <v>37.15415147181604</v>
       </c>
       <c r="D11" t="n">
-        <v>1.676783041344269</v>
+        <v>1.626942793429319</v>
       </c>
       <c r="E11" t="n">
-        <v>9.875998239536202</v>
+        <v>9.688107508864087</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529538094123143</v>
+        <v>0.7530066627730809</v>
       </c>
       <c r="G11" t="n">
-        <v>25.90980421963577</v>
+        <v>25.13699057140651</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63587523296645</v>
+        <v>34.63830648756172</v>
       </c>
       <c r="I11" t="n">
-        <v>3.234152195043504</v>
+        <v>3.280696864904172</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705961308826963</v>
+        <v>4.706291642331754</v>
       </c>
       <c r="K11" t="n">
-        <v>19.20847195323452</v>
+        <v>20.16965746872936</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51925269954259</v>
+        <v>42.56698409577378</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8923385860359</v>
+        <v>99.89079303631917</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.34543750665065</v>
+        <v>77.40160571337226</v>
       </c>
       <c r="C12" t="n">
-        <v>36.21863657468088</v>
+        <v>35.23196306092244</v>
       </c>
       <c r="D12" t="n">
-        <v>1.569098051437188</v>
+        <v>1.520332388509948</v>
       </c>
       <c r="E12" t="n">
-        <v>9.691453426297002</v>
+        <v>9.509454066065837</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538182016578561</v>
+        <v>0.7538942766406949</v>
       </c>
       <c r="G12" t="n">
-        <v>24.24584595127858</v>
+        <v>23.48981234602874</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67563727626137</v>
+        <v>34.67913672547196</v>
       </c>
       <c r="I12" t="n">
-        <v>2.698220839357053</v>
+        <v>2.737136681650735</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7113637603616</v>
+        <v>4.711839229004341</v>
       </c>
       <c r="K12" t="n">
-        <v>21.65456249334935</v>
+        <v>22.59839428662773</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03696337099633</v>
+        <v>42.07851218398029</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91016243902655</v>
+        <v>99.90886953153046</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.90278195881316</v>
+        <v>74.85613735842462</v>
       </c>
       <c r="C13" t="n">
-        <v>34.19231297718829</v>
+        <v>33.10818259474905</v>
       </c>
       <c r="D13" t="n">
-        <v>1.462596511315694</v>
+        <v>1.409655170783894</v>
       </c>
       <c r="E13" t="n">
-        <v>9.408775452142796</v>
+        <v>9.197728842886226</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545632989334815</v>
+        <v>0.7546607875763419</v>
       </c>
       <c r="G13" t="n">
-        <v>22.60017445675691</v>
+        <v>21.77980005199771</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70991175094014</v>
+        <v>34.71439622851172</v>
       </c>
       <c r="I13" t="n">
-        <v>2.250739870389883</v>
+        <v>2.283266354316577</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716020618334259</v>
+        <v>4.716629922352135</v>
       </c>
       <c r="K13" t="n">
-        <v>24.09721804118684</v>
+        <v>25.1438626415754</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63551840275385</v>
+        <v>41.67192318918524</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92504942112896</v>
+        <v>99.92396842550968</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.01155301887898</v>
+        <v>82.3060887535613</v>
       </c>
       <c r="C14" t="n">
-        <v>38.60237760625802</v>
+        <v>37.7066465663511</v>
       </c>
       <c r="D14" t="n">
-        <v>1.464326539980218</v>
+        <v>1.411391648963165</v>
       </c>
       <c r="E14" t="n">
-        <v>11.8561017965166</v>
+        <v>11.7477425315644</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554558322646178</v>
+        <v>0.7555904135001411</v>
       </c>
       <c r="G14" t="n">
-        <v>24.57215416433474</v>
+        <v>23.8383707566311</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69621543131341</v>
+        <v>36.78890036458545</v>
       </c>
       <c r="I14" t="n">
-        <v>2.945700302815546</v>
+        <v>3.041652953941146</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721598951653861</v>
+        <v>4.72244008437588</v>
       </c>
       <c r="K14" t="n">
-        <v>16.98844698112104</v>
+        <v>17.69391124643871</v>
       </c>
       <c r="L14" t="n">
-        <v>44.31110140911947</v>
+        <v>44.49817849669114</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90192599649853</v>
+        <v>99.89873630948097</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.26440374603898</v>
+        <v>81.49017787151583</v>
       </c>
       <c r="C15" t="n">
-        <v>38.31001410231389</v>
+        <v>37.35963626777186</v>
       </c>
       <c r="D15" t="n">
-        <v>1.436882801461683</v>
+        <v>1.381698609682437</v>
       </c>
       <c r="E15" t="n">
-        <v>12.04343254431278</v>
+        <v>11.92348226997134</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562080011643908</v>
+        <v>0.7563746351911973</v>
       </c>
       <c r="G15" t="n">
-        <v>24.11163408543743</v>
+        <v>23.33685604256488</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73275198422354</v>
+        <v>36.82708329165882</v>
       </c>
       <c r="I15" t="n">
-        <v>2.457194322161714</v>
+        <v>2.537341552502188</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726300007277442</v>
+        <v>4.727341469944981</v>
       </c>
       <c r="K15" t="n">
-        <v>17.73559625396103</v>
+        <v>18.50982212848415</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87256463531355</v>
+        <v>44.04605124391229</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91817499158847</v>
+        <v>99.9155096401683</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.85384988546247</v>
+        <v>78.95618887208443</v>
       </c>
       <c r="C16" t="n">
-        <v>36.27888056098892</v>
+        <v>35.21683110693704</v>
       </c>
       <c r="D16" t="n">
-        <v>1.345894243055817</v>
+        <v>1.287296034103819</v>
       </c>
       <c r="E16" t="n">
-        <v>11.62236826548119</v>
+        <v>11.46155086115768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756854925941966</v>
+        <v>0.7570504303313956</v>
       </c>
       <c r="G16" t="n">
-        <v>22.58479917307578</v>
+        <v>21.74239882817143</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76417631108934</v>
+        <v>36.85998704432087</v>
       </c>
       <c r="I16" t="n">
-        <v>2.049413679681099</v>
+        <v>2.116340484428005</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730343287137288</v>
+        <v>4.731565189571221</v>
       </c>
       <c r="K16" t="n">
-        <v>20.14615011453752</v>
+        <v>21.04381112791559</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50671392663575</v>
+        <v>43.66887605535562</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93174460216218</v>
+        <v>99.92951829020825</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.6958441980785</v>
+        <v>80.72795877141567</v>
       </c>
       <c r="C17" t="n">
-        <v>37.61553410266169</v>
+        <v>36.49870848695812</v>
       </c>
       <c r="D17" t="n">
-        <v>1.347012533375235</v>
+        <v>1.288423033767761</v>
       </c>
       <c r="E17" t="n">
-        <v>12.45507702533542</v>
+        <v>12.27402764829345</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574837892729831</v>
+        <v>0.7577132115083492</v>
       </c>
       <c r="G17" t="n">
-        <v>23.08721513284616</v>
+        <v>22.21049841839026</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27837377618275</v>
+        <v>37.34132175403658</v>
       </c>
       <c r="I17" t="n">
-        <v>2.036408258109821</v>
+        <v>2.120267133492086</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734273682956144</v>
+        <v>4.735707571927181</v>
       </c>
       <c r="K17" t="n">
-        <v>18.30415580192149</v>
+        <v>19.27204122858433</v>
       </c>
       <c r="L17" t="n">
-        <v>44.01248617437693</v>
+        <v>44.15863653414288</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9321760789601</v>
+        <v>99.92938624968532</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.34098488476393</v>
+        <v>78.33796270776611</v>
       </c>
       <c r="C18" t="n">
-        <v>35.57476364780826</v>
+        <v>34.43514779462861</v>
       </c>
       <c r="D18" t="n">
-        <v>1.261924573744031</v>
+        <v>1.203247928643911</v>
       </c>
       <c r="E18" t="n">
-        <v>11.95135217770365</v>
+        <v>11.7573190041166</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580242297259858</v>
+        <v>0.7582833066013461</v>
       </c>
       <c r="G18" t="n">
-        <v>21.62884412251992</v>
+        <v>20.7422061820218</v>
       </c>
       <c r="H18" t="n">
-        <v>37.30497070339903</v>
+        <v>37.36941695413956</v>
       </c>
       <c r="I18" t="n">
-        <v>1.698217641883897</v>
+        <v>1.768218665984486</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737651435787411</v>
+        <v>4.739270666258411</v>
       </c>
       <c r="K18" t="n">
-        <v>20.65901511523606</v>
+        <v>21.66203729223389</v>
       </c>
       <c r="L18" t="n">
-        <v>43.70965434089708</v>
+        <v>43.84391860387384</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9434331039414</v>
+        <v>99.94110369073633</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.45057898692025</v>
+        <v>77.41478607155466</v>
       </c>
       <c r="C19" t="n">
-        <v>34.94560276722267</v>
+        <v>33.78299229044379</v>
       </c>
       <c r="D19" t="n">
-        <v>1.230415384633911</v>
+        <v>1.171012481179286</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88894249640377</v>
+        <v>11.68815446927448</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584803076004694</v>
+        <v>0.7587648681220065</v>
       </c>
       <c r="G19" t="n">
-        <v>21.08879018120725</v>
+        <v>20.18651497178673</v>
       </c>
       <c r="H19" t="n">
-        <v>37.32741585894799</v>
+        <v>37.39314907786952</v>
       </c>
       <c r="I19" t="n">
-        <v>1.416032835623933</v>
+        <v>1.474909777560084</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740501922502933</v>
+        <v>4.742280425762539</v>
       </c>
       <c r="K19" t="n">
-        <v>21.54942101307974</v>
+        <v>22.58521392844534</v>
       </c>
       <c r="L19" t="n">
-        <v>43.45780350742302</v>
+        <v>43.58266132431369</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95282728772543</v>
+        <v>99.95086754320282</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.96278121697364</v>
+        <v>74.85850158175978</v>
       </c>
       <c r="C20" t="n">
-        <v>32.67550182706876</v>
+        <v>31.45301088078429</v>
       </c>
       <c r="D20" t="n">
-        <v>1.141524150816333</v>
+        <v>1.081019180193987</v>
       </c>
       <c r="E20" t="n">
-        <v>11.22680017795298</v>
+        <v>10.99487065315362</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588732593402291</v>
+        <v>0.7591803640681495</v>
       </c>
       <c r="G20" t="n">
-        <v>19.56523268807227</v>
+        <v>18.63516419893181</v>
       </c>
       <c r="H20" t="n">
-        <v>37.34675436102316</v>
+        <v>37.41362538417747</v>
       </c>
       <c r="I20" t="n">
-        <v>1.180638708892231</v>
+        <v>1.229764525808816</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742957870876431</v>
+        <v>4.744877275425933</v>
       </c>
       <c r="K20" t="n">
-        <v>24.03721878302638</v>
+        <v>25.14149841824023</v>
       </c>
       <c r="L20" t="n">
-        <v>43.24794514447086</v>
+        <v>43.36452098493213</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96066575456599</v>
+        <v>99.95903028395665</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.92245120317276</v>
+        <v>80.87342432875393</v>
       </c>
       <c r="C21" t="n">
-        <v>36.36482319481289</v>
+        <v>35.17066345862546</v>
       </c>
       <c r="D21" t="n">
-        <v>1.142322488046871</v>
+        <v>1.081814289113168</v>
       </c>
       <c r="E21" t="n">
-        <v>13.21536576013349</v>
+        <v>13.00324259486524</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594039855414733</v>
+        <v>0.7597387547884965</v>
       </c>
       <c r="G21" t="n">
-        <v>21.27316309252481</v>
+        <v>20.35173647114784</v>
       </c>
       <c r="H21" t="n">
-        <v>39.06712046449879</v>
+        <v>39.14400955006795</v>
       </c>
       <c r="I21" t="n">
-        <v>1.718800502793115</v>
+        <v>1.784515451343137</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746274909634207</v>
+        <v>4.748367217428101</v>
       </c>
       <c r="K21" t="n">
-        <v>18.07754879682724</v>
+        <v>19.12657567124608</v>
       </c>
       <c r="L21" t="n">
-        <v>45.50037469898636</v>
+        <v>45.6433207410272</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94274669062651</v>
+        <v>99.94055987089874</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_16_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.8025857915228</v>
+        <v>45.12864427299346</v>
       </c>
       <c r="M2" t="n">
-        <v>98.62154691756766</v>
+        <v>98.64838594157067</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.88667804994832</v>
+        <v>88.06877261413202</v>
       </c>
       <c r="C3" t="n">
-        <v>45.83025897996025</v>
+        <v>45.92500322392783</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228444092243481</v>
+        <v>2.228839725050715</v>
       </c>
       <c r="E3" t="n">
-        <v>5.642577711680765</v>
+        <v>5.706599073573941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428146974144938</v>
+        <v>0.7429465750169051</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94040094444508</v>
+        <v>33.97139444243032</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16947608106671</v>
+        <v>34.17554245077763</v>
       </c>
       <c r="I3" t="n">
-        <v>6.520372664257194</v>
+        <v>6.600034253426838</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642591858840587</v>
+        <v>4.643416093855657</v>
       </c>
       <c r="K3" t="n">
-        <v>12.11332195005169</v>
+        <v>11.93122738586799</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82234103547232</v>
+        <v>48.90687360342341</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7659219654843</v>
+        <v>106.7631042132192</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.80201670835841</v>
+        <v>87.16770602746021</v>
       </c>
       <c r="C4" t="n">
-        <v>42.37518341867408</v>
+        <v>42.66538465348711</v>
       </c>
       <c r="D4" t="n">
-        <v>2.175173085434642</v>
+        <v>2.185512614914863</v>
       </c>
       <c r="E4" t="n">
-        <v>6.415192672692334</v>
+        <v>6.514270179710429</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443678986862555</v>
+        <v>0.7445124606611824</v>
       </c>
       <c r="G4" t="n">
-        <v>33.12905488640417</v>
+        <v>33.31101391711365</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24092333956775</v>
+        <v>34.24757319041439</v>
       </c>
       <c r="I4" t="n">
-        <v>5.445005458784162</v>
+        <v>5.511620785513295</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652299366789097</v>
+        <v>4.653202879132389</v>
       </c>
       <c r="K4" t="n">
-        <v>13.19798329164159</v>
+        <v>12.83229397253982</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24571182678829</v>
+        <v>44.31898708915566</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81887853710397</v>
+        <v>99.81666571518258</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.40563820018058</v>
+        <v>86.12215135322681</v>
       </c>
       <c r="C5" t="n">
-        <v>41.82366079320402</v>
+        <v>42.47525738504358</v>
       </c>
       <c r="D5" t="n">
-        <v>2.106098324623406</v>
+        <v>2.134915368481722</v>
       </c>
       <c r="E5" t="n">
-        <v>6.969064345104014</v>
+        <v>7.130323143493658</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456884847595829</v>
+        <v>0.745838348135357</v>
       </c>
       <c r="G5" t="n">
-        <v>32.07700916300676</v>
+        <v>32.53982386833525</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30167029894081</v>
+        <v>34.30856401422642</v>
       </c>
       <c r="I5" t="n">
-        <v>4.545554553998607</v>
+        <v>4.601196934708407</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660553029747393</v>
+        <v>4.661489675845981</v>
       </c>
       <c r="K5" t="n">
-        <v>14.59436179981944</v>
+        <v>13.87784864677321</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43072725534365</v>
+        <v>43.49379339080785</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84874984836711</v>
+        <v>99.84689942262463</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.85180854218532</v>
+        <v>84.84361871303392</v>
       </c>
       <c r="C6" t="n">
-        <v>40.97535768088721</v>
+        <v>41.91142321807372</v>
       </c>
       <c r="D6" t="n">
-        <v>2.02963221225554</v>
+        <v>2.072745268864534</v>
       </c>
       <c r="E6" t="n">
-        <v>7.348317641756566</v>
+        <v>7.562702852151768</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468130478793268</v>
+        <v>0.7469635969771161</v>
       </c>
       <c r="G6" t="n">
-        <v>30.91238918377473</v>
+        <v>31.59224340623064</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35340020244903</v>
+        <v>34.36032546094734</v>
       </c>
       <c r="I6" t="n">
-        <v>3.793674704824328</v>
+        <v>3.840115646755545</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667581549245792</v>
+        <v>4.668522481106975</v>
       </c>
       <c r="K6" t="n">
-        <v>16.14819145781469</v>
+        <v>15.15638128696609</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75018545702038</v>
+        <v>42.80438446899607</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87373459572227</v>
+        <v>99.87218897403588</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.04844813694746</v>
+        <v>83.3986126792793</v>
       </c>
       <c r="C7" t="n">
-        <v>39.76069094498725</v>
+        <v>41.06299848585215</v>
       </c>
       <c r="D7" t="n">
-        <v>1.941280952294683</v>
+        <v>2.00265825490179</v>
       </c>
       <c r="E7" t="n">
-        <v>7.556017279441429</v>
+        <v>7.841012959397167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747773459184226</v>
+        <v>0.747920214314705</v>
       </c>
       <c r="G7" t="n">
-        <v>29.56675202040329</v>
+        <v>30.52399539814817</v>
       </c>
       <c r="H7" t="n">
-        <v>34.3975791224744</v>
+        <v>34.40432985847642</v>
       </c>
       <c r="I7" t="n">
-        <v>3.165461183248021</v>
+        <v>3.204194654574142</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673584119901412</v>
+        <v>4.674501339466905</v>
       </c>
       <c r="K7" t="n">
-        <v>17.95155186305254</v>
+        <v>16.6013873207207</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18237733904843</v>
+        <v>42.2289443143506</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89462014708823</v>
+        <v>99.89333012092345</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.91927108860294</v>
+        <v>88.12472200765328</v>
       </c>
       <c r="C8" t="n">
-        <v>42.03080721064757</v>
+        <v>43.3483892898191</v>
       </c>
       <c r="D8" t="n">
-        <v>1.94548116001168</v>
+        <v>2.006843670021091</v>
       </c>
       <c r="E8" t="n">
-        <v>9.368323506818077</v>
+        <v>9.656003502432673</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493913619664679</v>
+        <v>0.749483315041133</v>
       </c>
       <c r="G8" t="n">
-        <v>30.05855016757058</v>
+        <v>31.02665389186925</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47200265045753</v>
+        <v>34.47623249189211</v>
       </c>
       <c r="I8" t="n">
-        <v>5.641826229488183</v>
+        <v>5.525234417389933</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683696012290424</v>
+        <v>4.68427071900708</v>
       </c>
       <c r="K8" t="n">
-        <v>13.08072891139706</v>
+        <v>11.87527799234671</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70080901874313</v>
+        <v>44.59254234622482</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81234514078776</v>
+        <v>99.81620962839064</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.66411987230012</v>
+        <v>86.0112953583797</v>
       </c>
       <c r="C9" t="n">
-        <v>40.65018195638179</v>
+        <v>42.09295139917251</v>
       </c>
       <c r="D9" t="n">
-        <v>1.842846806938502</v>
+        <v>1.91090079236781</v>
       </c>
       <c r="E9" t="n">
-        <v>9.659135342789481</v>
+        <v>9.963136207968144</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750781094212851</v>
+        <v>0.7508230853116959</v>
       </c>
       <c r="G9" t="n">
-        <v>28.47280371359426</v>
+        <v>29.54333633066279</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53593033379115</v>
+        <v>34.537861924338</v>
       </c>
       <c r="I9" t="n">
-        <v>4.710240742143571</v>
+        <v>4.612592734533173</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692381838830318</v>
+        <v>4.692644283198099</v>
       </c>
       <c r="K9" t="n">
-        <v>15.33588012769989</v>
+        <v>13.98870464162028</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85722052065477</v>
+        <v>43.7648652253908</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84328260473643</v>
+        <v>99.84652126618359</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.30159915017585</v>
+        <v>83.82477928519994</v>
       </c>
       <c r="C10" t="n">
-        <v>39.01724633848632</v>
+        <v>40.62231822292693</v>
       </c>
       <c r="D10" t="n">
-        <v>1.736694992280172</v>
+        <v>1.812790932968523</v>
       </c>
       <c r="E10" t="n">
-        <v>9.757990809524125</v>
+        <v>10.0932254351517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519765585712773</v>
+        <v>0.7519724878257825</v>
       </c>
       <c r="G10" t="n">
-        <v>26.83271091194158</v>
+        <v>28.02651631302304</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59092169427876</v>
+        <v>34.59073443998599</v>
       </c>
       <c r="I10" t="n">
-        <v>3.931450692509453</v>
+        <v>3.849711627333746</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699853491070482</v>
+        <v>4.69982804891114</v>
       </c>
       <c r="K10" t="n">
-        <v>17.69840084982416</v>
+        <v>16.17522071480007</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15351279107445</v>
+        <v>43.07433348631375</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86915997938492</v>
+        <v>99.87187242404075</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.83034253127065</v>
+        <v>81.40591533075805</v>
       </c>
       <c r="C11" t="n">
-        <v>37.15415147181604</v>
+        <v>38.80032338499018</v>
       </c>
       <c r="D11" t="n">
-        <v>1.626942793429319</v>
+        <v>1.705223371714673</v>
       </c>
       <c r="E11" t="n">
-        <v>9.688107508864087</v>
+        <v>10.029698125246</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530066627730809</v>
+        <v>0.7529615931930964</v>
       </c>
       <c r="G11" t="n">
-        <v>25.13699057140651</v>
+        <v>26.36347621534538</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63830648756172</v>
+        <v>34.63623328688243</v>
       </c>
       <c r="I11" t="n">
-        <v>3.280696864904172</v>
+        <v>3.212312780919602</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706291642331754</v>
+        <v>4.706009957456852</v>
       </c>
       <c r="K11" t="n">
-        <v>20.16965746872936</v>
+        <v>18.59408466924196</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56698409577378</v>
+        <v>42.49865551167525</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89079303631917</v>
+        <v>99.8930635659074</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.40160571337226</v>
+        <v>78.92206040098955</v>
       </c>
       <c r="C12" t="n">
-        <v>35.23196306092244</v>
+        <v>36.81365892863616</v>
       </c>
       <c r="D12" t="n">
-        <v>1.520332388509948</v>
+        <v>1.595854301941228</v>
       </c>
       <c r="E12" t="n">
-        <v>9.509454066065837</v>
+        <v>9.833076118693382</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538942766406949</v>
+        <v>0.7538138707153866</v>
       </c>
       <c r="G12" t="n">
-        <v>23.48981234602874</v>
+        <v>24.67258403224837</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67913672547196</v>
+        <v>34.67543805290778</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737136681650735</v>
+        <v>2.679957332512227</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711839229004341</v>
+        <v>4.711336691971167</v>
       </c>
       <c r="K12" t="n">
-        <v>22.59839428662773</v>
+        <v>21.07793959901045</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07851218398029</v>
+        <v>42.01917056177228</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90886953153046</v>
+        <v>99.91076908941889</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.85613735842462</v>
+        <v>76.45636600896279</v>
       </c>
       <c r="C13" t="n">
-        <v>33.10818259474905</v>
+        <v>34.76185022775387</v>
       </c>
       <c r="D13" t="n">
-        <v>1.409655170783894</v>
+        <v>1.488308300028367</v>
       </c>
       <c r="E13" t="n">
-        <v>9.197728842886226</v>
+        <v>9.542995678071378</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546607875763419</v>
+        <v>0.7545485518987548</v>
       </c>
       <c r="G13" t="n">
-        <v>21.77980005199771</v>
+        <v>23.00987725112198</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71439622851172</v>
+        <v>34.70923338734271</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283266354316577</v>
+        <v>2.235474391132386</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716629922352135</v>
+        <v>4.715928449367218</v>
       </c>
       <c r="K13" t="n">
-        <v>25.1438626415754</v>
+        <v>23.5436339910372</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67192318918524</v>
+        <v>41.62007252197247</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92396842550968</v>
+        <v>99.92555674076354</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.3060887535613</v>
+        <v>83.38188788787494</v>
       </c>
       <c r="C14" t="n">
-        <v>37.7066465663511</v>
+        <v>39.16479655827754</v>
       </c>
       <c r="D14" t="n">
-        <v>1.411391648963165</v>
+        <v>1.489943083005096</v>
       </c>
       <c r="E14" t="n">
-        <v>11.7477425315644</v>
+        <v>11.9693809679576</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555904135001411</v>
+        <v>0.7553773607737281</v>
       </c>
       <c r="G14" t="n">
-        <v>23.8383707566311</v>
+        <v>24.99311442063864</v>
       </c>
       <c r="H14" t="n">
-        <v>36.78890036458545</v>
+        <v>36.70532132726078</v>
       </c>
       <c r="I14" t="n">
-        <v>3.041652953941146</v>
+        <v>2.747642223403293</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72244008437588</v>
+        <v>4.721108504835801</v>
       </c>
       <c r="K14" t="n">
-        <v>17.69391124643871</v>
+        <v>16.61811211212506</v>
       </c>
       <c r="L14" t="n">
-        <v>44.49817849669114</v>
+        <v>44.12560374699007</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89873630948097</v>
+        <v>99.90851241739267</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.49017787151583</v>
+        <v>82.52220087569715</v>
       </c>
       <c r="C15" t="n">
-        <v>37.35963626777186</v>
+        <v>38.72974579566994</v>
       </c>
       <c r="D15" t="n">
-        <v>1.381698609682437</v>
+        <v>1.457980660789314</v>
       </c>
       <c r="E15" t="n">
-        <v>11.92348226997134</v>
+        <v>12.09458274971402</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563746351911973</v>
+        <v>0.7560766433396194</v>
       </c>
       <c r="G15" t="n">
-        <v>23.33685604256488</v>
+        <v>24.4569593924958</v>
       </c>
       <c r="H15" t="n">
-        <v>36.82708329165882</v>
+        <v>36.73930088848738</v>
       </c>
       <c r="I15" t="n">
-        <v>2.537341552502188</v>
+        <v>2.291821519998378</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727341469944981</v>
+        <v>4.725479020872622</v>
       </c>
       <c r="K15" t="n">
-        <v>18.50982212848415</v>
+        <v>17.47779912430286</v>
       </c>
       <c r="L15" t="n">
-        <v>44.04605124391229</v>
+        <v>43.71613168493266</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9155096401683</v>
+        <v>99.92367660490547</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.95618887208443</v>
+        <v>79.96947031259162</v>
       </c>
       <c r="C16" t="n">
-        <v>35.21683110693704</v>
+        <v>36.53117742767746</v>
       </c>
       <c r="D16" t="n">
-        <v>1.287296034103819</v>
+        <v>1.361145831608231</v>
       </c>
       <c r="E16" t="n">
-        <v>11.46155086115768</v>
+        <v>11.60985793230537</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570504303313956</v>
+        <v>0.7566790167090532</v>
       </c>
       <c r="G16" t="n">
-        <v>21.74239882817143</v>
+        <v>22.83259937953179</v>
       </c>
       <c r="H16" t="n">
-        <v>36.85998704432087</v>
+        <v>36.76857143488211</v>
       </c>
       <c r="I16" t="n">
-        <v>2.116340484428005</v>
+        <v>1.911372863123495</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731565189571221</v>
+        <v>4.729243854431583</v>
       </c>
       <c r="K16" t="n">
-        <v>21.04381112791559</v>
+        <v>20.03052968740838</v>
       </c>
       <c r="L16" t="n">
-        <v>43.66887605535562</v>
+        <v>43.37463117602531</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92951829020825</v>
+        <v>99.93633829111116</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.72795877141567</v>
+        <v>81.63358175867519</v>
       </c>
       <c r="C17" t="n">
-        <v>36.49870848695812</v>
+        <v>37.7531703086137</v>
       </c>
       <c r="D17" t="n">
-        <v>1.288423033767761</v>
+        <v>1.362191617856615</v>
       </c>
       <c r="E17" t="n">
-        <v>12.27402764829345</v>
+        <v>12.37248065584158</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577132115083492</v>
+        <v>0.757260383151751</v>
       </c>
       <c r="G17" t="n">
-        <v>22.21049841839026</v>
+        <v>23.29024390915721</v>
       </c>
       <c r="H17" t="n">
-        <v>37.34132175403658</v>
+        <v>37.23692315516624</v>
       </c>
       <c r="I17" t="n">
-        <v>2.120267133492086</v>
+        <v>1.881604642803347</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735707571927181</v>
+        <v>4.732877394698444</v>
       </c>
       <c r="K17" t="n">
-        <v>19.27204122858433</v>
+        <v>18.36641824132482</v>
       </c>
       <c r="L17" t="n">
-        <v>44.15863653414288</v>
+        <v>43.81773944702575</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92938624968532</v>
+        <v>99.93732799696429</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.33796270776611</v>
+        <v>79.19504808852766</v>
       </c>
       <c r="C18" t="n">
-        <v>34.43514779462861</v>
+        <v>35.60497687402676</v>
       </c>
       <c r="D18" t="n">
-        <v>1.203247928643911</v>
+        <v>1.273315360547385</v>
       </c>
       <c r="E18" t="n">
-        <v>11.7573190041166</v>
+        <v>11.82674412934211</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582833066013461</v>
+        <v>0.7577604865476755</v>
       </c>
       <c r="G18" t="n">
-        <v>20.7422061820218</v>
+        <v>21.7706708305018</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36941695413956</v>
+        <v>37.26151484401991</v>
       </c>
       <c r="I18" t="n">
-        <v>1.768218665984486</v>
+        <v>1.5690393966458</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739270666258411</v>
+        <v>4.736003040922972</v>
       </c>
       <c r="K18" t="n">
-        <v>21.66203729223389</v>
+        <v>20.80495191147235</v>
       </c>
       <c r="L18" t="n">
-        <v>43.84391860387384</v>
+        <v>43.53780441886747</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94110369073633</v>
+        <v>99.94773320436657</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.41478607155466</v>
+        <v>78.17934173119095</v>
       </c>
       <c r="C19" t="n">
-        <v>33.78299229044379</v>
+        <v>34.81980946121585</v>
       </c>
       <c r="D19" t="n">
-        <v>1.171012481179286</v>
+        <v>1.236459318471347</v>
       </c>
       <c r="E19" t="n">
-        <v>11.68815446927448</v>
+        <v>11.70422294689152</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587648681220065</v>
+        <v>0.7581865792380137</v>
       </c>
       <c r="G19" t="n">
-        <v>20.18651497178673</v>
+        <v>21.14051997784294</v>
       </c>
       <c r="H19" t="n">
-        <v>37.39314907786952</v>
+        <v>37.28246718897299</v>
       </c>
       <c r="I19" t="n">
-        <v>1.474909777560084</v>
+        <v>1.318819599536553</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742280425762539</v>
+        <v>4.738666120237585</v>
       </c>
       <c r="K19" t="n">
-        <v>22.58521392844534</v>
+        <v>21.82065826880905</v>
       </c>
       <c r="L19" t="n">
-        <v>43.58266132431369</v>
+        <v>43.31559632207083</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95086754320282</v>
+        <v>99.95606405209574</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.85850158175978</v>
+        <v>75.5834437215297</v>
       </c>
       <c r="C20" t="n">
-        <v>31.45301088078429</v>
+        <v>32.42666020160709</v>
       </c>
       <c r="D20" t="n">
-        <v>1.081019180193987</v>
+        <v>1.142834559403282</v>
       </c>
       <c r="E20" t="n">
-        <v>10.99487065315362</v>
+        <v>11.00123683302501</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591803640681495</v>
+        <v>0.7585542362512514</v>
       </c>
       <c r="G20" t="n">
-        <v>18.63516419893181</v>
+        <v>19.53975878826643</v>
       </c>
       <c r="H20" t="n">
-        <v>37.41362538417747</v>
+        <v>37.30054606415779</v>
       </c>
       <c r="I20" t="n">
-        <v>1.229764525808816</v>
+        <v>1.099549263855608</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744877275425933</v>
+        <v>4.740963976570321</v>
       </c>
       <c r="K20" t="n">
-        <v>25.14149841824023</v>
+        <v>24.4165562784703</v>
       </c>
       <c r="L20" t="n">
-        <v>43.36452098493213</v>
+        <v>43.12014964215771</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95903028395665</v>
+        <v>99.9633661222351</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.87342432875393</v>
+        <v>81.56323953566589</v>
       </c>
       <c r="C21" t="n">
-        <v>35.17066345862546</v>
+        <v>36.23213640646564</v>
       </c>
       <c r="D21" t="n">
-        <v>1.081814289113168</v>
+        <v>1.143520664766366</v>
       </c>
       <c r="E21" t="n">
-        <v>13.00324259486524</v>
+        <v>13.02627211561866</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597387547884965</v>
+        <v>0.7590096373636868</v>
       </c>
       <c r="G21" t="n">
-        <v>20.35173647114784</v>
+        <v>21.32508609876638</v>
       </c>
       <c r="H21" t="n">
-        <v>39.14400955006795</v>
+        <v>39.09653613533671</v>
       </c>
       <c r="I21" t="n">
-        <v>1.784515451343137</v>
+        <v>1.469004650291053</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748367217428101</v>
+        <v>4.743810233523042</v>
       </c>
       <c r="K21" t="n">
-        <v>19.12657567124608</v>
+        <v>18.4367604643341</v>
       </c>
       <c r="L21" t="n">
-        <v>45.6433207410272</v>
+        <v>45.28216568731561</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94055987089874</v>
+        <v>99.95106255811535</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_16_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.12864427299346</v>
+        <v>43.63719559875089</v>
       </c>
       <c r="M2" t="n">
-        <v>98.64838594157067</v>
+        <v>96.42070954255018</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06877261413202</v>
+        <v>81.43883797028627</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92500322392783</v>
+        <v>43.19439352584184</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228839725050715</v>
+        <v>2.178394039073598</v>
       </c>
       <c r="E3" t="n">
-        <v>5.706599073573941</v>
+        <v>4.142883192054921</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429465750169051</v>
+        <v>0.7376061027824511</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97139444243032</v>
+        <v>32.7666770043987</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17554245077763</v>
+        <v>33.92988072799275</v>
       </c>
       <c r="I3" t="n">
-        <v>6.600034253426838</v>
+        <v>3.073358761593546</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643416093855657</v>
+        <v>4.610038142390319</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93122738586799</v>
+        <v>18.56116202971371</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90687360342341</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631042132192</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16770602746021</v>
+        <v>88.47884973908447</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66538465348711</v>
+        <v>42.76614360890527</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185512614914863</v>
+        <v>2.18410567393112</v>
       </c>
       <c r="E4" t="n">
-        <v>6.514270179710429</v>
+        <v>6.505919333163171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445124606611824</v>
+        <v>0.7395400672774904</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31101391711365</v>
+        <v>33.44870911888925</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24757319041439</v>
+        <v>34.01884309476456</v>
       </c>
       <c r="I4" t="n">
-        <v>5.511620785513295</v>
+        <v>6.959607030574574</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653202879132389</v>
+        <v>4.622125420484315</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83229397253982</v>
+        <v>11.52115026091552</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31898708915566</v>
+        <v>45.48132589599224</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81666571518258</v>
+        <v>99.76861976581303</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12215135322681</v>
+        <v>87.28736664173015</v>
       </c>
       <c r="C5" t="n">
-        <v>42.47525738504358</v>
+        <v>42.65340318348646</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134915368481722</v>
+        <v>2.127060521102549</v>
       </c>
       <c r="E5" t="n">
-        <v>7.130323143493658</v>
+        <v>7.304753377823122</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745838348135357</v>
+        <v>0.7411816223910405</v>
       </c>
       <c r="G5" t="n">
-        <v>32.53982386833525</v>
+        <v>32.5750853073769</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30856401422642</v>
+        <v>34.09435462998786</v>
       </c>
       <c r="I5" t="n">
-        <v>4.601196934708407</v>
+        <v>5.812546043104657</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661489675845981</v>
+        <v>4.632385139944003</v>
       </c>
       <c r="K5" t="n">
-        <v>13.87784864677321</v>
+        <v>12.71263335826988</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49379339080785</v>
+        <v>44.44064104072768</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84689942262463</v>
+        <v>99.80667758248403</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.84361871303392</v>
+        <v>85.87070649245135</v>
       </c>
       <c r="C6" t="n">
-        <v>41.91142321807372</v>
+        <v>42.13871874095717</v>
       </c>
       <c r="D6" t="n">
-        <v>2.072745268864534</v>
+        <v>2.059198382606495</v>
       </c>
       <c r="E6" t="n">
-        <v>7.562702852151768</v>
+        <v>7.880520008295892</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469635969771161</v>
+        <v>0.7425778649407943</v>
       </c>
       <c r="G6" t="n">
-        <v>31.59224340623064</v>
+        <v>31.53580366554372</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36032546094734</v>
+        <v>34.15858178727653</v>
       </c>
       <c r="I6" t="n">
-        <v>3.840115646755545</v>
+        <v>4.852913127907956</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668522481106975</v>
+        <v>4.641111655879964</v>
       </c>
       <c r="K6" t="n">
-        <v>15.15638128696609</v>
+        <v>14.12929350754863</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80438446899607</v>
+        <v>43.57052813918575</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87218897403588</v>
+        <v>99.83854038769155</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.3986126792793</v>
+        <v>84.2334010641857</v>
       </c>
       <c r="C7" t="n">
-        <v>41.06299848585215</v>
+        <v>41.25481020533066</v>
       </c>
       <c r="D7" t="n">
-        <v>2.00265825490179</v>
+        <v>1.981079012453856</v>
       </c>
       <c r="E7" t="n">
-        <v>7.841012959397167</v>
+        <v>8.25665450437493</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747920214314705</v>
+        <v>0.7437681562438071</v>
       </c>
       <c r="G7" t="n">
-        <v>30.52399539814817</v>
+        <v>30.33943660328368</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40432985847642</v>
+        <v>34.21333518721512</v>
       </c>
       <c r="I7" t="n">
-        <v>3.204194654574142</v>
+        <v>4.050576624090512</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674501339466905</v>
+        <v>4.648550976523794</v>
       </c>
       <c r="K7" t="n">
-        <v>16.6013873207207</v>
+        <v>15.76659893581431</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2289443143506</v>
+        <v>42.84378771641313</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89333012092345</v>
+        <v>99.86519685755809</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.12472200765328</v>
+        <v>82.39570421493862</v>
       </c>
       <c r="C8" t="n">
-        <v>43.3483892898191</v>
+        <v>40.04582151378843</v>
       </c>
       <c r="D8" t="n">
-        <v>2.006843670021091</v>
+        <v>1.893944341049924</v>
       </c>
       <c r="E8" t="n">
-        <v>9.656003502432673</v>
+        <v>8.456847802294542</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749483315041133</v>
+        <v>0.7447852027705023</v>
       </c>
       <c r="G8" t="n">
-        <v>31.02665389186925</v>
+        <v>29.00500379046364</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47623249189211</v>
+        <v>34.2601193274431</v>
       </c>
       <c r="I8" t="n">
-        <v>5.525234417389933</v>
+        <v>3.380096233601275</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68427071900708</v>
+        <v>4.654907517315639</v>
       </c>
       <c r="K8" t="n">
-        <v>11.87527799234671</v>
+        <v>17.60429578506139</v>
       </c>
       <c r="L8" t="n">
-        <v>44.59254234622482</v>
+        <v>42.23736668381434</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81620962839064</v>
+        <v>99.88748398266416</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.0112953583797</v>
+        <v>80.55954925746235</v>
       </c>
       <c r="C9" t="n">
-        <v>42.09295139917251</v>
+        <v>38.73388398932475</v>
       </c>
       <c r="D9" t="n">
-        <v>1.91090079236781</v>
+        <v>1.807688720137605</v>
       </c>
       <c r="E9" t="n">
-        <v>9.963136207968144</v>
+        <v>8.54170445911986</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508230853116959</v>
+        <v>0.745654257322202</v>
       </c>
       <c r="G9" t="n">
-        <v>29.54333633066279</v>
+        <v>27.68403328605922</v>
       </c>
       <c r="H9" t="n">
-        <v>34.537861924338</v>
+        <v>34.30009583682129</v>
       </c>
       <c r="I9" t="n">
-        <v>4.612592734533173</v>
+        <v>2.820033589738401</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692644283198099</v>
+        <v>4.660339108263763</v>
       </c>
       <c r="K9" t="n">
-        <v>13.98870464162028</v>
+        <v>19.44045074253765</v>
       </c>
       <c r="L9" t="n">
-        <v>43.7648652253908</v>
+        <v>41.73177370609314</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84652126618359</v>
+        <v>99.90610843795554</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.82477928519994</v>
+        <v>85.50076450551971</v>
       </c>
       <c r="C10" t="n">
-        <v>40.62231822292693</v>
+        <v>42.06067413113149</v>
       </c>
       <c r="D10" t="n">
-        <v>1.812790932968523</v>
+        <v>1.809797148366159</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0932254351517</v>
+        <v>10.44369084234484</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519724878257825</v>
+        <v>0.746523963741989</v>
       </c>
       <c r="G10" t="n">
-        <v>28.02651631302304</v>
+        <v>29.10972035337795</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59073443998599</v>
+        <v>35.73349966028753</v>
       </c>
       <c r="I10" t="n">
-        <v>3.849711627333746</v>
+        <v>2.99175776401382</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69982804891114</v>
+        <v>4.665774773387431</v>
       </c>
       <c r="K10" t="n">
-        <v>16.17522071480007</v>
+        <v>14.49923549448029</v>
       </c>
       <c r="L10" t="n">
-        <v>43.07433348631375</v>
+        <v>43.34048129631604</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87187242404075</v>
+        <v>99.90039092192781</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.40591533075805</v>
+        <v>85.21315169808356</v>
       </c>
       <c r="C11" t="n">
-        <v>38.80032338499018</v>
+        <v>42.15993035441063</v>
       </c>
       <c r="D11" t="n">
-        <v>1.705223371714673</v>
+        <v>1.793232531711515</v>
       </c>
       <c r="E11" t="n">
-        <v>10.029698125246</v>
+        <v>10.79555874469886</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529615931930964</v>
+        <v>0.7472683295057798</v>
       </c>
       <c r="G11" t="n">
-        <v>26.36347621534538</v>
+        <v>28.865908794537</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63623328688243</v>
+        <v>35.79175222108776</v>
       </c>
       <c r="I11" t="n">
-        <v>3.212312780919602</v>
+        <v>2.549004017131527</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706009957456852</v>
+        <v>4.670427059411124</v>
       </c>
       <c r="K11" t="n">
-        <v>18.59408466924196</v>
+        <v>14.78684830191644</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49865551167525</v>
+        <v>42.96833917987145</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8930635659074</v>
+        <v>99.91511783619852</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.92206040098955</v>
+        <v>83.33030686349382</v>
       </c>
       <c r="C12" t="n">
-        <v>36.81365892863616</v>
+        <v>40.67315190157612</v>
       </c>
       <c r="D12" t="n">
-        <v>1.595854301941228</v>
+        <v>1.713240844677052</v>
       </c>
       <c r="E12" t="n">
-        <v>9.833076118693382</v>
+        <v>10.66832486439848</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538138707153866</v>
+        <v>0.747903822534742</v>
       </c>
       <c r="G12" t="n">
-        <v>24.67258403224837</v>
+        <v>27.5782716914703</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67543805290778</v>
+        <v>35.8221902955153</v>
       </c>
       <c r="I12" t="n">
-        <v>2.679957332512227</v>
+        <v>2.125976454055804</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711336691971167</v>
+        <v>4.674398890842138</v>
       </c>
       <c r="K12" t="n">
-        <v>21.07793959901045</v>
+        <v>16.66969313650618</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01917056177228</v>
+        <v>42.58634929477515</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91076908941889</v>
+        <v>99.92919433285745</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.45636600896279</v>
+        <v>84.57347434642745</v>
       </c>
       <c r="C13" t="n">
-        <v>34.76185022775387</v>
+        <v>41.69426292561003</v>
       </c>
       <c r="D13" t="n">
-        <v>1.488308300028367</v>
+        <v>1.714584831403968</v>
       </c>
       <c r="E13" t="n">
-        <v>9.542995678071378</v>
+        <v>11.33620511690478</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545485518987548</v>
+        <v>0.7484905309439066</v>
       </c>
       <c r="G13" t="n">
-        <v>23.00987725112198</v>
+        <v>27.92769036137975</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70923338734271</v>
+        <v>36.17807607553132</v>
       </c>
       <c r="I13" t="n">
-        <v>2.235474391132386</v>
+        <v>1.990361611864318</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715928449367218</v>
+        <v>4.678065818399417</v>
       </c>
       <c r="K13" t="n">
-        <v>23.5436339910372</v>
+        <v>15.42652565357253</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62007252197247</v>
+        <v>42.81291803895094</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92555674076354</v>
+        <v>99.9337066181335</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.38188788787494</v>
+        <v>82.65712246269179</v>
       </c>
       <c r="C14" t="n">
-        <v>39.16479655827754</v>
+        <v>40.08705806965565</v>
       </c>
       <c r="D14" t="n">
-        <v>1.489943083005096</v>
+        <v>1.635496507511427</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9693809679576</v>
+        <v>11.08992631099055</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553773607737281</v>
+        <v>0.7489915175362363</v>
       </c>
       <c r="G14" t="n">
-        <v>24.99311442063864</v>
+        <v>26.63947517341336</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70532132726078</v>
+        <v>36.20229111941072</v>
       </c>
       <c r="I14" t="n">
-        <v>2.747642223403293</v>
+        <v>1.659744849228032</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721108504835801</v>
+        <v>4.681196984601477</v>
       </c>
       <c r="K14" t="n">
-        <v>16.61811211212506</v>
+        <v>17.34287753730822</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12560374699007</v>
+        <v>42.51477657048433</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90851241739267</v>
+        <v>99.9447121774482</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.52220087569715</v>
+        <v>81.85527020777114</v>
       </c>
       <c r="C15" t="n">
-        <v>38.72974579566994</v>
+        <v>39.51839601606238</v>
       </c>
       <c r="D15" t="n">
-        <v>1.457980660789314</v>
+        <v>1.601933669958004</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09458274971402</v>
+        <v>11.09689586809734</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560766433396194</v>
+        <v>0.7494207557465034</v>
       </c>
       <c r="G15" t="n">
-        <v>24.4569593924958</v>
+        <v>26.09279324921032</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73930088848738</v>
+        <v>36.22303822573146</v>
       </c>
       <c r="I15" t="n">
-        <v>2.291821519998378</v>
+        <v>1.407308715611866</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725479020872622</v>
+        <v>4.683879723415646</v>
       </c>
       <c r="K15" t="n">
-        <v>17.47779912430286</v>
+        <v>18.14472979222885</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71613168493266</v>
+        <v>42.28999076952503</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92367660490547</v>
+        <v>99.95311657781626</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.96947031259162</v>
+        <v>79.61109313063338</v>
       </c>
       <c r="C16" t="n">
-        <v>36.53117742767746</v>
+        <v>37.49232600970937</v>
       </c>
       <c r="D16" t="n">
-        <v>1.361145831608231</v>
+        <v>1.509999897558905</v>
       </c>
       <c r="E16" t="n">
-        <v>11.60985793230537</v>
+        <v>10.65560890187399</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7566790167090532</v>
+        <v>0.7497889290657851</v>
       </c>
       <c r="G16" t="n">
-        <v>22.83259937953179</v>
+        <v>24.59534740559274</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76857143488211</v>
+        <v>36.24083377798402</v>
       </c>
       <c r="I16" t="n">
-        <v>1.911372863123495</v>
+        <v>1.173333411896776</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729243854431583</v>
+        <v>4.686180806661157</v>
       </c>
       <c r="K16" t="n">
-        <v>20.03052968740838</v>
+        <v>20.38890686936663</v>
       </c>
       <c r="L16" t="n">
-        <v>43.37463117602531</v>
+        <v>42.07967521215699</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93633829111116</v>
+        <v>99.96090809123299</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.63358175867519</v>
+        <v>84.26292791262011</v>
       </c>
       <c r="C17" t="n">
-        <v>37.7531703086137</v>
+        <v>40.53648114105732</v>
       </c>
       <c r="D17" t="n">
-        <v>1.362191617856615</v>
+        <v>1.510809291032569</v>
       </c>
       <c r="E17" t="n">
-        <v>12.37248065584158</v>
+        <v>12.28791648008404</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757260383151751</v>
+        <v>0.7501908325803431</v>
       </c>
       <c r="G17" t="n">
-        <v>23.29024390915721</v>
+        <v>26.00929299133836</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23692315516624</v>
+        <v>37.66102160300574</v>
       </c>
       <c r="I17" t="n">
-        <v>1.881604642803347</v>
+        <v>1.35500401095191</v>
       </c>
       <c r="J17" t="n">
-        <v>4.732877394698444</v>
+        <v>4.688692703627145</v>
       </c>
       <c r="K17" t="n">
-        <v>18.36641824132482</v>
+        <v>15.73707208737989</v>
       </c>
       <c r="L17" t="n">
-        <v>43.81773944702575</v>
+        <v>43.68130416863527</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93732799696429</v>
+        <v>99.95485739707249</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.19504808852766</v>
+        <v>85.93705318528697</v>
       </c>
       <c r="C18" t="n">
-        <v>35.60497687402676</v>
+        <v>41.27122960230808</v>
       </c>
       <c r="D18" t="n">
-        <v>1.273315360547385</v>
+        <v>1.512123923273737</v>
       </c>
       <c r="E18" t="n">
-        <v>11.82674412934211</v>
+        <v>12.89899947506466</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577604865476755</v>
+        <v>0.7508436118962982</v>
       </c>
       <c r="G18" t="n">
-        <v>21.7706708305018</v>
+        <v>26.14517479448693</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26151484401991</v>
+        <v>37.69379237925693</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5690393966458</v>
+        <v>2.24334642695655</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736003040922972</v>
+        <v>4.692772574351864</v>
       </c>
       <c r="K18" t="n">
-        <v>20.80495191147235</v>
+        <v>14.06294681471301</v>
       </c>
       <c r="L18" t="n">
-        <v>43.53780441886747</v>
+        <v>44.59111038051613</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94773320436657</v>
+        <v>99.92528679753723</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.17934173119095</v>
+        <v>83.46075168095709</v>
       </c>
       <c r="C19" t="n">
-        <v>34.81980946121585</v>
+        <v>39.14241619302459</v>
       </c>
       <c r="D19" t="n">
-        <v>1.236459318471347</v>
+        <v>1.420856969038479</v>
       </c>
       <c r="E19" t="n">
-        <v>11.70422294689152</v>
+        <v>12.43226590470659</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7581865792380137</v>
+        <v>0.7514046410436431</v>
       </c>
       <c r="G19" t="n">
-        <v>21.14051997784294</v>
+        <v>24.56713582908575</v>
       </c>
       <c r="H19" t="n">
-        <v>37.28246718897299</v>
+        <v>37.72195712070731</v>
       </c>
       <c r="I19" t="n">
-        <v>1.318819599536553</v>
+        <v>1.870852209852544</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738666120237585</v>
+        <v>4.69627900652277</v>
       </c>
       <c r="K19" t="n">
-        <v>21.82065826880905</v>
+        <v>16.53924831904291</v>
       </c>
       <c r="L19" t="n">
-        <v>43.31559632207083</v>
+        <v>44.25602030940591</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95606405209574</v>
+        <v>99.93768482147341</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.5834437215297</v>
+        <v>80.81099499224086</v>
       </c>
       <c r="C20" t="n">
-        <v>32.42666020160709</v>
+        <v>36.78174723985997</v>
       </c>
       <c r="D20" t="n">
-        <v>1.142834559403282</v>
+        <v>1.323714996411917</v>
       </c>
       <c r="E20" t="n">
-        <v>11.00123683302501</v>
+        <v>11.84229733610269</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585542362512514</v>
+        <v>0.7518881669820572</v>
       </c>
       <c r="G20" t="n">
-        <v>19.53975878826643</v>
+        <v>22.88751565040087</v>
       </c>
       <c r="H20" t="n">
-        <v>37.30054606415779</v>
+        <v>37.74623105211433</v>
       </c>
       <c r="I20" t="n">
-        <v>1.099549263855608</v>
+        <v>1.56004674659116</v>
       </c>
       <c r="J20" t="n">
-        <v>4.740963976570321</v>
+        <v>4.699301043637858</v>
       </c>
       <c r="K20" t="n">
-        <v>24.4165562784703</v>
+        <v>19.18900500775914</v>
       </c>
       <c r="L20" t="n">
-        <v>43.12014964215771</v>
+        <v>43.97727963544053</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9633661222351</v>
+        <v>99.94803188305964</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.56323953566589</v>
+        <v>78.28914039443391</v>
       </c>
       <c r="C21" t="n">
-        <v>36.23213640646564</v>
+        <v>34.50023471133935</v>
       </c>
       <c r="D21" t="n">
-        <v>1.143520664766366</v>
+        <v>1.231806255027966</v>
       </c>
       <c r="E21" t="n">
-        <v>13.02627211561866</v>
+        <v>11.23685108054616</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590096373636868</v>
+        <v>0.7523045828728617</v>
       </c>
       <c r="G21" t="n">
-        <v>21.32508609876638</v>
+        <v>21.29837995084639</v>
       </c>
       <c r="H21" t="n">
-        <v>39.09653613533671</v>
+        <v>37.76713593015113</v>
       </c>
       <c r="I21" t="n">
-        <v>1.469004650291053</v>
+        <v>1.300758952034014</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743810233523042</v>
+        <v>4.701903642955386</v>
       </c>
       <c r="K21" t="n">
-        <v>18.4367604643341</v>
+        <v>21.71085960556609</v>
       </c>
       <c r="L21" t="n">
-        <v>45.28216568731561</v>
+        <v>43.74557105124482</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95106255811535</v>
+        <v>99.95666536815025</v>
       </c>
     </row>
   </sheetData>
